--- a/artfynd/A 48476-2024 artfynd.xlsx
+++ b/artfynd/A 48476-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121275618</v>
+        <v>121275617</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,16 +718,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551362</v>
+        <v>551429</v>
       </c>
       <c r="R2" t="n">
-        <v>6714832</v>
+        <v>6714814</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,6 +775,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275613</v>
+        <v>121275615</v>
       </c>
       <c r="B3" t="n">
-        <v>90687</v>
+        <v>91137</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551441</v>
+        <v>551435</v>
       </c>
       <c r="R3" t="n">
-        <v>6714847</v>
+        <v>6714843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121275612</v>
+        <v>121275613</v>
       </c>
       <c r="B4" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551425</v>
+        <v>551441</v>
       </c>
       <c r="R4" t="n">
-        <v>6714846</v>
+        <v>6714847</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121275616</v>
+        <v>121275612</v>
       </c>
       <c r="B5" t="n">
-        <v>97025</v>
+        <v>90697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551579</v>
+        <v>551425</v>
       </c>
       <c r="R5" t="n">
-        <v>6714828</v>
+        <v>6714846</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1103,7 @@
         <v>121275620</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1197,7 +1205,7 @@
         <v>121275614</v>
       </c>
       <c r="B7" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,7 +1307,7 @@
         <v>121275619</v>
       </c>
       <c r="B8" t="n">
-        <v>105176</v>
+        <v>105186</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,10 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121275617</v>
+        <v>121275618</v>
       </c>
       <c r="B9" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,7 +1441,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1441,23 +1449,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551429</v>
+        <v>551362</v>
       </c>
       <c r="R9" t="n">
-        <v>6714814</v>
+        <v>6714832</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1499,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121275615</v>
+        <v>121275616</v>
       </c>
       <c r="B10" t="n">
-        <v>91127</v>
+        <v>97035</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,25 +1529,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551435</v>
+        <v>551579</v>
       </c>
       <c r="R10" t="n">
-        <v>6714843</v>
+        <v>6714828</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 48476-2024 artfynd.xlsx
+++ b/artfynd/A 48476-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121275617</v>
+        <v>121275619</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>105186</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,54 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551429</v>
+        <v>551440</v>
       </c>
       <c r="R2" t="n">
-        <v>6714814</v>
+        <v>6714841</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275615</v>
+        <v>121275620</v>
       </c>
       <c r="B3" t="n">
-        <v>91137</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551435</v>
+        <v>551329</v>
       </c>
       <c r="R3" t="n">
-        <v>6714843</v>
+        <v>6714849</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121275613</v>
+        <v>121275616</v>
       </c>
       <c r="B4" t="n">
-        <v>90697</v>
+        <v>97035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551441</v>
+        <v>551579</v>
       </c>
       <c r="R4" t="n">
-        <v>6714847</v>
+        <v>6714828</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121275612</v>
+        <v>121275613</v>
       </c>
       <c r="B5" t="n">
         <v>90697</v>
@@ -1038,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551425</v>
+        <v>551441</v>
       </c>
       <c r="R5" t="n">
-        <v>6714846</v>
+        <v>6714847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121275620</v>
+        <v>121275614</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551329</v>
+        <v>551479</v>
       </c>
       <c r="R6" t="n">
-        <v>6714849</v>
+        <v>6714866</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121275614</v>
+        <v>121275617</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1214,38 +1197,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551479</v>
+        <v>551429</v>
       </c>
       <c r="R7" t="n">
-        <v>6714866</v>
+        <v>6714814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1285,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121275619</v>
+        <v>121275618</v>
       </c>
       <c r="B8" t="n">
-        <v>105186</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1316,38 +1316,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551440</v>
+        <v>551362</v>
       </c>
       <c r="R8" t="n">
-        <v>6714841</v>
+        <v>6714832</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121275618</v>
+        <v>121275612</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1418,47 +1427,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551362</v>
+        <v>551425</v>
       </c>
       <c r="R9" t="n">
-        <v>6714832</v>
+        <v>6714846</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121275616</v>
+        <v>121275615</v>
       </c>
       <c r="B10" t="n">
-        <v>97035</v>
+        <v>91137</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,25 +1529,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551579</v>
+        <v>551435</v>
       </c>
       <c r="R10" t="n">
-        <v>6714828</v>
+        <v>6714843</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 48476-2024 artfynd.xlsx
+++ b/artfynd/A 48476-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121275619</v>
+        <v>121275618</v>
       </c>
       <c r="B2" t="n">
-        <v>105186</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551440</v>
+        <v>551362</v>
       </c>
       <c r="R2" t="n">
-        <v>6714841</v>
+        <v>6714832</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275620</v>
+        <v>121275612</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>90709</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551329</v>
+        <v>551425</v>
       </c>
       <c r="R3" t="n">
-        <v>6714849</v>
+        <v>6714846</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121275616</v>
+        <v>121275615</v>
       </c>
       <c r="B4" t="n">
-        <v>97035</v>
+        <v>91149</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551579</v>
+        <v>551435</v>
       </c>
       <c r="R4" t="n">
-        <v>6714828</v>
+        <v>6714843</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121275613</v>
+        <v>121275614</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551441</v>
+        <v>551479</v>
       </c>
       <c r="R5" t="n">
-        <v>6714847</v>
+        <v>6714866</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121275614</v>
+        <v>121275619</v>
       </c>
       <c r="B6" t="n">
-        <v>90697</v>
+        <v>105199</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551479</v>
+        <v>551440</v>
       </c>
       <c r="R6" t="n">
-        <v>6714866</v>
+        <v>6714841</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121275617</v>
+        <v>121275620</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,54 +1206,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551429</v>
+        <v>551329</v>
       </c>
       <c r="R7" t="n">
-        <v>6714814</v>
+        <v>6714849</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1278,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1304,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121275618</v>
+        <v>121275617</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,7 +1331,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1347,16 +1339,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551362</v>
+        <v>551429</v>
       </c>
       <c r="R8" t="n">
-        <v>6714832</v>
+        <v>6714814</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,6 +1396,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121275612</v>
+        <v>121275613</v>
       </c>
       <c r="B9" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551425</v>
+        <v>551441</v>
       </c>
       <c r="R9" t="n">
-        <v>6714846</v>
+        <v>6714847</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121275615</v>
+        <v>121275616</v>
       </c>
       <c r="B10" t="n">
-        <v>91137</v>
+        <v>97048</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,25 +1529,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551435</v>
+        <v>551579</v>
       </c>
       <c r="R10" t="n">
-        <v>6714843</v>
+        <v>6714828</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 48476-2024 artfynd.xlsx
+++ b/artfynd/A 48476-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121275618</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275612</v>
+        <v>121275615</v>
       </c>
       <c r="B3" t="n">
-        <v>90709</v>
+        <v>91150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551425</v>
+        <v>551435</v>
       </c>
       <c r="R3" t="n">
-        <v>6714846</v>
+        <v>6714843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121275615</v>
+        <v>121275614</v>
       </c>
       <c r="B4" t="n">
-        <v>91149</v>
+        <v>90710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551435</v>
+        <v>551479</v>
       </c>
       <c r="R4" t="n">
-        <v>6714843</v>
+        <v>6714866</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121275614</v>
+        <v>121275616</v>
       </c>
       <c r="B5" t="n">
-        <v>90709</v>
+        <v>97049</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551479</v>
+        <v>551579</v>
       </c>
       <c r="R5" t="n">
-        <v>6714866</v>
+        <v>6714828</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121275619</v>
+        <v>121275612</v>
       </c>
       <c r="B6" t="n">
-        <v>105199</v>
+        <v>90710</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551440</v>
+        <v>551425</v>
       </c>
       <c r="R6" t="n">
-        <v>6714841</v>
+        <v>6714846</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121275620</v>
+        <v>121275613</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551329</v>
+        <v>551441</v>
       </c>
       <c r="R7" t="n">
-        <v>6714849</v>
+        <v>6714847</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
         <v>121275617</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121275613</v>
+        <v>121275620</v>
       </c>
       <c r="B9" t="n">
-        <v>90709</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551441</v>
+        <v>551329</v>
       </c>
       <c r="R9" t="n">
-        <v>6714847</v>
+        <v>6714849</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121275616</v>
+        <v>121275619</v>
       </c>
       <c r="B10" t="n">
-        <v>97048</v>
+        <v>105200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,21 +1533,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551579</v>
+        <v>551440</v>
       </c>
       <c r="R10" t="n">
-        <v>6714828</v>
+        <v>6714841</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 48476-2024 artfynd.xlsx
+++ b/artfynd/A 48476-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121275618</v>
+        <v>121275620</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551362</v>
+        <v>551329</v>
       </c>
       <c r="R2" t="n">
-        <v>6714832</v>
+        <v>6714849</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275615</v>
+        <v>121275616</v>
       </c>
       <c r="B3" t="n">
-        <v>91150</v>
+        <v>97052</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551435</v>
+        <v>551579</v>
       </c>
       <c r="R3" t="n">
-        <v>6714843</v>
+        <v>6714828</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121275614</v>
+        <v>121275619</v>
       </c>
       <c r="B4" t="n">
-        <v>90710</v>
+        <v>105203</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551479</v>
+        <v>551440</v>
       </c>
       <c r="R4" t="n">
-        <v>6714866</v>
+        <v>6714841</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121275616</v>
+        <v>121275618</v>
       </c>
       <c r="B5" t="n">
-        <v>97049</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +993,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551579</v>
+        <v>551362</v>
       </c>
       <c r="R5" t="n">
-        <v>6714828</v>
+        <v>6714832</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121275612</v>
+        <v>121275615</v>
       </c>
       <c r="B6" t="n">
-        <v>90710</v>
+        <v>91153</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551425</v>
+        <v>551435</v>
       </c>
       <c r="R6" t="n">
-        <v>6714846</v>
+        <v>6714843</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121275613</v>
+        <v>121275617</v>
       </c>
       <c r="B7" t="n">
-        <v>90710</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,38 +1206,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551441</v>
+        <v>551429</v>
       </c>
       <c r="R7" t="n">
-        <v>6714847</v>
+        <v>6714814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,6 +1294,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1296,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121275617</v>
+        <v>121275612</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>90713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,54 +1325,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551429</v>
+        <v>551425</v>
       </c>
       <c r="R8" t="n">
-        <v>6714814</v>
+        <v>6714846</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,7 +1397,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121275620</v>
+        <v>121275613</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>90713</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551329</v>
+        <v>551441</v>
       </c>
       <c r="R9" t="n">
-        <v>6714849</v>
+        <v>6714847</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121275619</v>
+        <v>121275614</v>
       </c>
       <c r="B10" t="n">
-        <v>105200</v>
+        <v>90713</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,25 +1529,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551440</v>
+        <v>551479</v>
       </c>
       <c r="R10" t="n">
-        <v>6714841</v>
+        <v>6714866</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 48476-2024 artfynd.xlsx
+++ b/artfynd/A 48476-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121275620</v>
+        <v>121275618</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551329</v>
+        <v>551362</v>
       </c>
       <c r="R2" t="n">
-        <v>6714849</v>
+        <v>6714832</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275616</v>
+        <v>121275614</v>
       </c>
       <c r="B3" t="n">
-        <v>97052</v>
+        <v>90713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551579</v>
+        <v>551479</v>
       </c>
       <c r="R3" t="n">
-        <v>6714828</v>
+        <v>6714866</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121275619</v>
+        <v>121275612</v>
       </c>
       <c r="B4" t="n">
-        <v>105203</v>
+        <v>90713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551440</v>
+        <v>551425</v>
       </c>
       <c r="R4" t="n">
-        <v>6714841</v>
+        <v>6714846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121275618</v>
+        <v>121275613</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,47 +1002,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551362</v>
+        <v>551441</v>
       </c>
       <c r="R5" t="n">
-        <v>6714832</v>
+        <v>6714847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121275612</v>
+        <v>121275619</v>
       </c>
       <c r="B8" t="n">
-        <v>90713</v>
+        <v>105203</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,25 +1325,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551425</v>
+        <v>551440</v>
       </c>
       <c r="R8" t="n">
-        <v>6714846</v>
+        <v>6714841</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121275613</v>
+        <v>121275620</v>
       </c>
       <c r="B9" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551441</v>
+        <v>551329</v>
       </c>
       <c r="R9" t="n">
-        <v>6714847</v>
+        <v>6714849</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121275614</v>
+        <v>121275616</v>
       </c>
       <c r="B10" t="n">
-        <v>90713</v>
+        <v>97052</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,25 +1529,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551479</v>
+        <v>551579</v>
       </c>
       <c r="R10" t="n">
-        <v>6714866</v>
+        <v>6714828</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 48476-2024 artfynd.xlsx
+++ b/artfynd/A 48476-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121275618</v>
+        <v>121275619</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>105209</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551362</v>
+        <v>551440</v>
       </c>
       <c r="R2" t="n">
-        <v>6714832</v>
+        <v>6714841</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275614</v>
+        <v>121275620</v>
       </c>
       <c r="B3" t="n">
-        <v>90713</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551479</v>
+        <v>551329</v>
       </c>
       <c r="R3" t="n">
-        <v>6714866</v>
+        <v>6714849</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121275612</v>
+        <v>121275614</v>
       </c>
       <c r="B4" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551425</v>
+        <v>551479</v>
       </c>
       <c r="R4" t="n">
-        <v>6714846</v>
+        <v>6714866</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +984,7 @@
         <v>121275613</v>
       </c>
       <c r="B5" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121275615</v>
+        <v>121275618</v>
       </c>
       <c r="B6" t="n">
-        <v>91153</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,34 +1099,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551435</v>
+        <v>551362</v>
       </c>
       <c r="R6" t="n">
-        <v>6714843</v>
+        <v>6714832</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121275617</v>
+        <v>121275615</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>91159</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,50 +1210,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551429</v>
+        <v>551435</v>
       </c>
       <c r="R7" t="n">
-        <v>6714814</v>
+        <v>6714843</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,7 +1278,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1313,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121275619</v>
+        <v>121275617</v>
       </c>
       <c r="B8" t="n">
-        <v>105203</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,38 +1308,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551440</v>
+        <v>551429</v>
       </c>
       <c r="R8" t="n">
-        <v>6714841</v>
+        <v>6714814</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,6 +1396,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121275620</v>
+        <v>121275616</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>97058</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,25 +1427,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551329</v>
+        <v>551579</v>
       </c>
       <c r="R9" t="n">
-        <v>6714849</v>
+        <v>6714828</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121275616</v>
+        <v>121275612</v>
       </c>
       <c r="B10" t="n">
-        <v>97052</v>
+        <v>90719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,25 +1529,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551579</v>
+        <v>551425</v>
       </c>
       <c r="R10" t="n">
-        <v>6714828</v>
+        <v>6714846</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 48476-2024 artfynd.xlsx
+++ b/artfynd/A 48476-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121275619</v>
+        <v>121275615</v>
       </c>
       <c r="B2" t="n">
-        <v>105209</v>
+        <v>91160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551440</v>
+        <v>551435</v>
       </c>
       <c r="R2" t="n">
-        <v>6714841</v>
+        <v>6714843</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275620</v>
+        <v>121275619</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>105210</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551329</v>
+        <v>551440</v>
       </c>
       <c r="R3" t="n">
-        <v>6714849</v>
+        <v>6714841</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121275614</v>
+        <v>121275616</v>
       </c>
       <c r="B4" t="n">
-        <v>90719</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551479</v>
+        <v>551579</v>
       </c>
       <c r="R4" t="n">
-        <v>6714866</v>
+        <v>6714828</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>121275613</v>
       </c>
       <c r="B5" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121275618</v>
+        <v>121275617</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1126,16 +1126,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551362</v>
+        <v>551429</v>
       </c>
       <c r="R6" t="n">
-        <v>6714832</v>
+        <v>6714814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,6 +1183,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1194,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121275615</v>
+        <v>121275612</v>
       </c>
       <c r="B7" t="n">
-        <v>91159</v>
+        <v>90720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1214,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551435</v>
+        <v>551425</v>
       </c>
       <c r="R7" t="n">
-        <v>6714843</v>
+        <v>6714846</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1304,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121275617</v>
+        <v>121275620</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,54 +1316,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551429</v>
+        <v>551329</v>
       </c>
       <c r="R8" t="n">
-        <v>6714814</v>
+        <v>6714849</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,7 +1388,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1415,10 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121275616</v>
+        <v>121275618</v>
       </c>
       <c r="B9" t="n">
-        <v>97058</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,38 +1418,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551579</v>
+        <v>551362</v>
       </c>
       <c r="R9" t="n">
-        <v>6714828</v>
+        <v>6714832</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121275612</v>
+        <v>121275614</v>
       </c>
       <c r="B10" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551425</v>
+        <v>551479</v>
       </c>
       <c r="R10" t="n">
-        <v>6714846</v>
+        <v>6714866</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 48476-2024 artfynd.xlsx
+++ b/artfynd/A 48476-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121275615</v>
+        <v>121275613</v>
       </c>
       <c r="B2" t="n">
-        <v>91160</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551435</v>
+        <v>551441</v>
       </c>
       <c r="R2" t="n">
-        <v>6714843</v>
+        <v>6714847</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121275616</v>
+        <v>121275618</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551579</v>
+        <v>551362</v>
       </c>
       <c r="R4" t="n">
-        <v>6714828</v>
+        <v>6714832</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121275613</v>
+        <v>121275615</v>
       </c>
       <c r="B5" t="n">
-        <v>90720</v>
+        <v>91160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551441</v>
+        <v>551435</v>
       </c>
       <c r="R5" t="n">
-        <v>6714847</v>
+        <v>6714843</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1202,7 +1211,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121275612</v>
+        <v>121275614</v>
       </c>
       <c r="B7" t="n">
         <v>90720</v>
@@ -1242,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551425</v>
+        <v>551479</v>
       </c>
       <c r="R7" t="n">
-        <v>6714846</v>
+        <v>6714866</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121275620</v>
+        <v>121275616</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1316,25 +1325,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1344,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551329</v>
+        <v>551579</v>
       </c>
       <c r="R8" t="n">
-        <v>6714849</v>
+        <v>6714828</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121275618</v>
+        <v>121275620</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1418,47 +1427,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551362</v>
+        <v>551329</v>
       </c>
       <c r="R9" t="n">
-        <v>6714832</v>
+        <v>6714849</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121275614</v>
+        <v>121275612</v>
       </c>
       <c r="B10" t="n">
         <v>90720</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551479</v>
+        <v>551425</v>
       </c>
       <c r="R10" t="n">
-        <v>6714866</v>
+        <v>6714846</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 48476-2024 artfynd.xlsx
+++ b/artfynd/A 48476-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275619</v>
+        <v>121275616</v>
       </c>
       <c r="B3" t="n">
-        <v>105210</v>
+        <v>97059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551440</v>
+        <v>551579</v>
       </c>
       <c r="R3" t="n">
-        <v>6714841</v>
+        <v>6714828</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121275618</v>
+        <v>121275620</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,47 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551362</v>
+        <v>551329</v>
       </c>
       <c r="R4" t="n">
-        <v>6714832</v>
+        <v>6714849</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121275615</v>
+        <v>121275617</v>
       </c>
       <c r="B5" t="n">
-        <v>91160</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,34 +997,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551435</v>
+        <v>551429</v>
       </c>
       <c r="R5" t="n">
-        <v>6714843</v>
+        <v>6714814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,6 +1081,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1092,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121275617</v>
+        <v>121275614</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,54 +1112,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551429</v>
+        <v>551479</v>
       </c>
       <c r="R6" t="n">
-        <v>6714814</v>
+        <v>6714866</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1184,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1211,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121275614</v>
+        <v>121275618</v>
       </c>
       <c r="B7" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,38 +1214,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551479</v>
+        <v>551362</v>
       </c>
       <c r="R7" t="n">
-        <v>6714866</v>
+        <v>6714832</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121275616</v>
+        <v>121275612</v>
       </c>
       <c r="B8" t="n">
-        <v>97059</v>
+        <v>90720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,25 +1325,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551579</v>
+        <v>551425</v>
       </c>
       <c r="R8" t="n">
-        <v>6714828</v>
+        <v>6714846</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121275620</v>
+        <v>121275619</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>105210</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,25 +1427,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551329</v>
+        <v>551440</v>
       </c>
       <c r="R9" t="n">
-        <v>6714849</v>
+        <v>6714841</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121275612</v>
+        <v>121275615</v>
       </c>
       <c r="B10" t="n">
-        <v>90720</v>
+        <v>91160</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,25 +1529,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551425</v>
+        <v>551435</v>
       </c>
       <c r="R10" t="n">
-        <v>6714846</v>
+        <v>6714843</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 48476-2024 artfynd.xlsx
+++ b/artfynd/A 48476-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275616</v>
+        <v>121275619</v>
       </c>
       <c r="B3" t="n">
-        <v>97059</v>
+        <v>105210</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551579</v>
+        <v>551440</v>
       </c>
       <c r="R3" t="n">
-        <v>6714828</v>
+        <v>6714841</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121275620</v>
+        <v>121275617</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551329</v>
+        <v>551429</v>
       </c>
       <c r="R4" t="n">
-        <v>6714849</v>
+        <v>6714814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +979,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121275617</v>
+        <v>121275615</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>91160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,50 +1014,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551429</v>
+        <v>551435</v>
       </c>
       <c r="R5" t="n">
-        <v>6714814</v>
+        <v>6714843</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1082,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1100,7 +1100,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121275614</v>
+        <v>121275612</v>
       </c>
       <c r="B6" t="n">
         <v>90720</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551479</v>
+        <v>551425</v>
       </c>
       <c r="R6" t="n">
-        <v>6714866</v>
+        <v>6714846</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121275618</v>
+        <v>121275616</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>97059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1214,47 +1214,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551362</v>
+        <v>551579</v>
       </c>
       <c r="R7" t="n">
-        <v>6714832</v>
+        <v>6714828</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,10 +1304,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121275612</v>
+        <v>121275618</v>
       </c>
       <c r="B8" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,38 +1316,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551425</v>
+        <v>551362</v>
       </c>
       <c r="R8" t="n">
-        <v>6714846</v>
+        <v>6714832</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121275619</v>
+        <v>121275620</v>
       </c>
       <c r="B9" t="n">
-        <v>105210</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,25 +1427,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551440</v>
+        <v>551329</v>
       </c>
       <c r="R9" t="n">
-        <v>6714841</v>
+        <v>6714849</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121275615</v>
+        <v>121275614</v>
       </c>
       <c r="B10" t="n">
-        <v>91160</v>
+        <v>90720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,25 +1529,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551435</v>
+        <v>551479</v>
       </c>
       <c r="R10" t="n">
-        <v>6714843</v>
+        <v>6714866</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 48476-2024 artfynd.xlsx
+++ b/artfynd/A 48476-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121275613</v>
+        <v>121275620</v>
       </c>
       <c r="B2" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551441</v>
+        <v>551329</v>
       </c>
       <c r="R2" t="n">
-        <v>6714847</v>
+        <v>6714849</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,50 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121275619</v>
+        <v>121275618</v>
       </c>
       <c r="B3" t="n">
-        <v>105210</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551440</v>
+        <v>551362</v>
       </c>
       <c r="R3" t="n">
-        <v>6714841</v>
+        <v>6714832</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,66 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121275617</v>
+        <v>121275612</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551429</v>
+        <v>551425</v>
       </c>
       <c r="R4" t="n">
-        <v>6714814</v>
+        <v>6714846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +957,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,37 +975,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121275615</v>
+        <v>121275613</v>
       </c>
       <c r="B5" t="n">
-        <v>91160</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551435</v>
+        <v>551441</v>
       </c>
       <c r="R5" t="n">
-        <v>6714843</v>
+        <v>6714847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,15 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121275612</v>
+        <v>121275614</v>
       </c>
       <c r="B6" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551425</v>
+        <v>551479</v>
       </c>
       <c r="R6" t="n">
-        <v>6714846</v>
+        <v>6714866</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,37 +1169,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121275616</v>
+        <v>121275615</v>
       </c>
       <c r="B7" t="n">
-        <v>97059</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1242,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551579</v>
+        <v>551435</v>
       </c>
       <c r="R7" t="n">
-        <v>6714828</v>
+        <v>6714843</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,15 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121275618</v>
+        <v>121275617</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1339,7 +1296,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1347,16 +1304,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Knätjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551362</v>
+        <v>551429</v>
       </c>
       <c r="R8" t="n">
-        <v>6714832</v>
+        <v>6714814</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,6 +1361,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1415,37 +1380,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121275620</v>
+        <v>121275619</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551329</v>
+        <v>551440</v>
       </c>
       <c r="R9" t="n">
-        <v>6714849</v>
+        <v>6714841</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,37 +1477,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121275614</v>
+        <v>121275616</v>
       </c>
       <c r="B10" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551479</v>
+        <v>551579</v>
       </c>
       <c r="R10" t="n">
-        <v>6714866</v>
+        <v>6714828</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 48476-2024 artfynd.xlsx
+++ b/artfynd/A 48476-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121275612</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121275613</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121275614</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121275615</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121275620</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121275617</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1377,6 +1412,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121275618</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1474,6 +1514,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121275619</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1571,8 +1616,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121275616</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>